--- a/build/report-suite/PO-Questions-Chris-ReportSuite-2026-08-03.xlsx
+++ b/build/report-suite/PO-Questions-Chris-ReportSuite-2026-08-03.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions for PO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="QA Internal Mapping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SUPERSEDED" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Questions for PO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="QA Internal Mapping" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="4">
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -75,6 +80,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -442,6 +450,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="220" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>SUPERSEDED 2026-08-04 - DO NOT SEND THIS FILE.
+The QA lead asked for one sheet with three tabs, so this sheet and the other two Chris Ward sheets were consolidated into a single workbook on 2026-08-04:
+build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
+Send that workbook, never this file. This one is kept only as the record of how its questions were derived and verified. Its content was carried across faithfully - four overlapping items across the three sheets were removed so nothing is asked twice, and every removal plus every text change is logged on the consolidated workbook's QA-only tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -993,7 +1028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1287,7 +1322,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Source</t>
@@ -1533,7 +1567,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Candidate question</t>
@@ -1544,7 +1577,6 @@
           <t>Already answered by</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="5" t="inlineStr">
@@ -1674,7 +1706,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1685,7 +1716,6 @@
           <t>Why it is not on the sheet</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
